--- a/光伏配储项目/电价数据/2026/大港站.xlsx
+++ b/光伏配储项目/电价数据/2026/大港站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.55424</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38009</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.74106</v>
+      </c>
+      <c r="D117" t="n">
+        <v>1.18893</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1.19745</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.23802</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1.25408</v>
+      </c>
+      <c r="H117" t="n">
+        <v>1.18878</v>
+      </c>
+      <c r="I117" t="n">
+        <v>1.18874</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44043</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.73594</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.7889299999999999</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.72153</v>
+      </c>
+      <c r="N117" t="n">
+        <v>1.18884</v>
+      </c>
+      <c r="O117" t="n">
+        <v>1.18873</v>
+      </c>
+      <c r="P117" t="n">
+        <v>1.18894</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.71482</v>
+      </c>
+      <c r="R117" t="n">
+        <v>1.18882</v>
+      </c>
+      <c r="S117" t="n">
+        <v>1.18886</v>
+      </c>
+      <c r="T117" t="n">
+        <v>1.189</v>
+      </c>
+      <c r="U117" t="n">
+        <v>1.18891</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.77085</v>
+      </c>
+      <c r="W117" t="n">
+        <v>1.18885</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39494</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.74378</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>1.18886</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>1.19284</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.78861</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>1.21723</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>1.2978</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.40483</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.88803</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.6958200000000001</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.6901799999999999</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.31736</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.47098</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.75822</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.78142</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.40431</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.39369</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>1.05028</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>1.03951</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>1.13118</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.76051</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.32585</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.72327</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.50874</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.41075</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.40704</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.41133</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.79313</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.9867</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.34921</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.53127</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.78543</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.43018</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.79369</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.7667</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.9623400000000001</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.92623</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>1.07761</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>1.35408</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.20924</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.24795</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.74909</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.25549</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>1.19724</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>1.10639</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>1.25656</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.5505</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>1.27158</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.28431</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.50061</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.34126</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.26014</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.44054</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.38102</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.31323</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.81817</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47924</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.41065</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.4127</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.4219</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.19272</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1.04627</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.18294</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53623</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5226499999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50627</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5162899999999999</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.81148</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.7137</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.7857999999999999</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.69231</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.68386</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.8077000000000001</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.75073</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.75091</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.75088</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.75093</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.7318</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.7945599999999999</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1.10265</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.46472</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.03722</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.78976</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.68338</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.7494700000000001</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.65097</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.6508400000000001</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.96235</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>1.17527</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.80057</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>1.13156</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>1.0607</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>1.02314</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.72754</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.55584</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.57869</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.6990599999999999</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.35213</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>1.20075</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1.26624</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.51622</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.31668</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>1.19626</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.67024</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>1.09281</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.84613</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.27935</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.1702</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.29724</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.62624</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.65289</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.5761499999999999</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.62739</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.2114</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>1.20339</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.21101</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>1.20416</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>1.00219</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.18364</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.19875</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.19538</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.67599</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.19864</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.20795</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.26503</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.56304</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.47911</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.20382</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.50642</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.26642</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.7564500000000001</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.7638400000000001</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.9141</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44059</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43462</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41383</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35426</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33341</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.7528400000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.9018200000000001</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.65312</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.75136</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.6510199999999999</v>
+      </c>
+      <c r="I119" t="n">
+        <v>1.5927</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.95163</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.94267</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.8926799999999999</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.7699199999999999</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.95163</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.74761</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.9516100000000001</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.6508400000000001</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37974</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.7506799999999999</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.65067</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.75093</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.74975</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.7099299999999999</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.7495499999999999</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.74888</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.6596900000000001</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.7080599999999999</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.83987</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.12035</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.8819400000000001</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.76752</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.71441</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.60956</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.3078</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.30098</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.6414500000000001</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.42646</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.7459600000000001</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>1.18478</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.56186</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.69716</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>1.19356</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.67246</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.19594</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>1.19992</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.80932</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.9750800000000001</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.20179</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>1.20184</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.9085700000000001</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.56336</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.4147</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.47719</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.6799500000000001</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>1.18916</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>1.05379</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>1.20028</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.44127</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.28351</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>1.19928</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.22356</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>1.21453</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.4491</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.29329</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.30829</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.67033</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.21704</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>1.21494</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>1.07128</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>1.10372</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.12459</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1.11066</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>1.23995</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>1.19574</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.28324</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>1.02443</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.7702899999999999</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.7276699999999999</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.5387799999999999</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.41308</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34314</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1.19549</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.93338</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.91679</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.8885299999999999</v>
+      </c>
+      <c r="H120" t="n">
+        <v>1.05787</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.7399</v>
+      </c>
+      <c r="J120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.90112</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.77001</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.97711</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.95026</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.88575</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.7501</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.75038</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.5405399999999999</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.6475299999999999</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.55031</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33379</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.53177</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.77008</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.75017</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.90111</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.74961</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.69314</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.65059</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.55126</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.6874600000000001</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.72457</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.94231</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>1.1966</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.33997</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.86336</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.5823</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.67253</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.91327</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.89501</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.19024</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.44749</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.7793</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.98819</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1.24882</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.70989</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.11816</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.53065</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.4928</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.6702899999999999</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>1.02631</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>1.12776</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>1.26625</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>1.19985</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>1.10091</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>1.01612</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>1.03532</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.9992799999999999</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>1.29693</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.47786</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.81467</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.38323</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>1.23471</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.86627</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>1.10713</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>1.18705</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>1.13445</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>1.1899</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>1.28653</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.3469</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>1.18974</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.30037</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>1.20426</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>1.19194</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>1.1861</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>1.21688</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>1.22894</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>1.21464</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>1.19169</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>1.19005</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.74317</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.5317799999999999</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.7473200000000001</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.33251</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32199</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.7501100000000001</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.49976</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.40629</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36484</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34515</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.34337</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.3431</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.34291</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.34285</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.34274</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.33738</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.33423</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.48475</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.51128</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.53061</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.40594</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.46485</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.34484</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.43344</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.46281</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.72862</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.86203</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.62534</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.71357</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.34599</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.7390099999999999</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.85958</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.71715</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.56024</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.55929</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.54787</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.6025499999999999</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.47891</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.10222</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.29332</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.28631</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.31559</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.55625</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.49205</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.5235700000000001</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.46912</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.65007</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.51248</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.49204</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.40322</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.49248</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.49573</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.60875</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.40642</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.5135</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.5124500000000001</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.40946</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.49153</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39844</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40988</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.38188</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.40546</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.3443</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.21941</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.99709</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1.0122</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.59946</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.79726</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.80186</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.72963</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.8014600000000001</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.36443</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.80302</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.80287</v>
+      </c>
+      <c r="N122" t="n">
+        <v>1.18875</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.80226</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.80211</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.80287</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.8034</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.8034</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.33847</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.27843</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.07493999999999999</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.3113</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04281</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04375</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04318</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04177</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.04665</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.27513</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.08406</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.29675</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.13122</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04294</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04452</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04647999999999999</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04627000000000001</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04506</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04233</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.30797</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04617</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04545</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.30588</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.30935</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.2689</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.28622</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.34261</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.29423</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.29762</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.36066</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.39325</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.43033</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.36541</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.36602</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.44865</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.79911</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.80161</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.36382</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.39435</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.39059</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.36475</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.39451</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.8008500000000001</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.8021900000000001</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.80203</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.36793</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.39776</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.36506</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33457</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.77127</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.70224</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4055299999999999</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34491</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.27879</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.30825</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.30677</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.30579</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.30439</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.30837</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.29128</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.28753</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17179</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16014</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15938</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23743</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.29379</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27503</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.30819</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.31134</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.31218</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.31567</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.31553</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.30462</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.32224</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.38901</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.7649400000000001</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.9019299999999999</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.69414</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.6682100000000001</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.68579</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.76849</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.96701</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.41291</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.36424</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.48414</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.7466799999999999</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.74962</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.9135700000000001</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.70023</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.54814</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.48519</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.45691</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.09425</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29705</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.37809</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.38137</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.74536</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.7507200000000001</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.65496</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.61442</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.48068</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.74013</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79104</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.79116</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.61091</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.75454</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>1.03101</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.43171</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.8614299999999999</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.46133</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.34832</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.81252</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.40676</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>1.06541</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.42711</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.78836</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.46568</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.7873600000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.80104</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5303600000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78769</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78555</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87858</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87914</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50259</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41209</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41215</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46079</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21926</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6393799999999999</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5414099999999999</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.8142999999999999</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.7999299999999999</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.8008099999999999</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.8001900000000001</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.80044</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.70568</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.80052</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.8012</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.6670900000000001</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.65078</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.67838</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38636</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.80213</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.8040700000000001</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.7997300000000001</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.7995</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.8012100000000001</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.80092</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.8012699999999999</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.7639900000000001</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.6690499999999999</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.79823</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.6507999999999999</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.60021</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43742</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59623</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.5648200000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>1.07798</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.6476000000000001</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.50915</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.57704</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.59678</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>1.00965</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.34252</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.31112</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.27305</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.5611799999999999</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.80023</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.57657</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.6565299999999999</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.55853</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.98982</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.78751</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.7362000000000001</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.6514800000000001</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.58366</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>1.0222</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>1.16181</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.5704600000000001</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.7575599999999999</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.7523300000000001</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.79738</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.70116</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.75118</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.9007200000000001</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.75039</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.7503200000000001</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.61036</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.59223</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.7512000000000001</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.79816</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.79908</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.7985099999999999</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.79518</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.79644</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.80259</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.7958999999999999</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.80288</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.8005</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.79635</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.7966599999999999</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.79845</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.7970700000000001</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.7995399999999999</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.80238</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.8108099999999999</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.80148</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.8003899999999999</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.80141</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.8020499999999999</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.8025</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.66642</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.95612</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.75076</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.9544400000000001</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.90064</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.95363</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.7848999999999999</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.78677</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.70217</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.7517699999999999</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.37525</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.36415</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.65076</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.66464</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.41128</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.53335</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.6302000000000001</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.75073</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.90081</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>1.15398</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.94178</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.56086</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.12598</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.86848</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.97694</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.8859400000000001</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.65439</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.8358300000000001</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>1.09777</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.74794</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.5342899999999999</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.4382</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.38196</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.37803</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.9045700000000001</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>1.21891</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.95478</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>1.23692</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.8081799999999999</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.83938</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.95085</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.76093</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.40844</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.39355</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.37647</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.3455299999999999</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.47809</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.39572</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.38155</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.36539</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.4449</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.38337</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.34448</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.37116</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.39765</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.50061</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.42046</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.41592</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34464</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59675</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.20062</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.51806</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70359</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79534</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64979</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5836399999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5005500000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.80365</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.43923</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.77052</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.19114</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.9351</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.6582100000000001</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.71557</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.57879</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.17771</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.63574</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.9229400000000001</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.60017</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.79649</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.54717</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.47056</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>1.43857</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>1.21989</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.54239</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.6166699999999999</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.87271</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.52933</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.76436</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>1.09702</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>1.09584</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.96347</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.99649</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.95036</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.18705</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>1.18555</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.88919</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>1.18557</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.63148</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.99794</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>1.04186</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>1.18559</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.97838</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>1.01931</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.6085</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.95084</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>1.00773</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>1.11496</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.91223</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.89986</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>1.1248</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.61377</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.98665</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>1.02409</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.75873</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38619</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36888</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33384</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.34364</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.90077</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.7505499999999999</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.75075</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.34571</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.34354</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.34346</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.34292</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.34338</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.34398</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.7046</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.6005499999999999</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.72687</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33721</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.3941</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.95925</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.7595</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.70769</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.75529</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.70528</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.75514</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.8358099999999999</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.72754</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.9055800000000001</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.7704500000000001</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>1.17023</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>1.47646</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.7725299999999999</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.7747200000000001</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.77647</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.71236</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.7154700000000001</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.77643</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.90883</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.91767</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.77249</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.65422</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.64781</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.65759</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.65988</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.3722200000000001</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.7001000000000001</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.37952</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.40324</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36158</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.4054</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.7006</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.70062</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45674</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43992</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4392799999999999</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.4442</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.70051</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.70363</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.70055</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34934</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.6122799999999999</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.55026</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46869</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41593</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.60064</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.90134</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.80136</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.8013899999999999</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.80137</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.82025</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.70114</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.74626</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.60088</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.50063</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.60088</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.50063</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.77223</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.81141</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.80136</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.77122</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.70099</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.70097</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.6533300000000001</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34604</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34866</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.3755</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29475</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.33351</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29399</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.32086</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.55869</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.29408</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.33224</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.35741</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.2822</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26677</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30023</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30819</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30662</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.47337</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30697</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31459</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.33553</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.31413</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.38394</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.48714</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.7054900000000001</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.60587</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.62658</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.84704</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>1.26791</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>1.16325</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.85027</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.39628</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.42853</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.70016</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.9380599999999999</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.16496</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.11891</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.01563</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.5411900000000001</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.43858</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.42935</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.39696</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.37968</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41952</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.49693</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.44725</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.41392</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.42594</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36025</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36608</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41871</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.56587</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.65223</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.64934</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.65224</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.60576</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.77754</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.5047900000000001</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.60577</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.5038</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34558</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.34676</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.60494</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.6756799999999999</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.77681</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.69875</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.77193</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>1.14579</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>1.48814</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.41501</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>1.31394</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>1.00135</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.99007</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.99165</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.56134</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.55223</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.9438200000000001</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>1.08358</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.79181</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.01059</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.77582</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.65637</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.64911</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.71641</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.79686</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.29454</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.76915</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.35702</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.49351</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.16533</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.9926799999999999</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.6583</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.63181</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.66544</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.67881</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.67388</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.65086</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.67536</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.20675</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.70829</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.79007</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.70558</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.71336</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.72151</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>1.6404</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.7558</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>1.019</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>1.12839</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.69942</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.70786</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.70163</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.78125</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.73141</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.82056</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.67187</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.46504</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>1.27692</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.65712</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.77213</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.6475700000000001</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.68098</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.34487</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.6419900000000001</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.79231</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1.37822</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.6678200000000001</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.77724</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.39242</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.68167</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.65434</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.81543</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.77806</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.77865</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.6738200000000001</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.34341</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.63328</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.34372</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.39817</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.40265</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.34492</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.42695</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.7538400000000001</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.49543</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.51366</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.52216</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29797</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34211</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.30128</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28471</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.34366</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.34154</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.34468</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.33615</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.45346</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.92996</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.48323</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.18962</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.9002</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.76158</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.44962</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.3942</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.45723</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.5002</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.45077</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.4917</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3677</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36162</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36793</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39307</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.4029700000000001</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36956</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34929</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35551</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.39034</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34292</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36932</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34229</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.34296</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.40591</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.40593</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30055</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.63119</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.4219</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.34391</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.39019</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.34676</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.34448</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.39098</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.45072</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.75342</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.42794</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.51811</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.70228</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.4986</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.4069</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.42018</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.42852</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.35448</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.4229</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5660499999999999</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38967</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.42651</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.45526</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35241</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.40161</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.66949</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.45186</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38358</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.43036</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40911</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38577</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38516</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65181</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83158</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47208</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40269</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45941</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34479</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.34678</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.7137899999999999</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.6788500000000001</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.6739299999999999</v>
+      </c>
+      <c r="F132" t="n">
+        <v>1.28414</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.66222</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.5802</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.5384800000000001</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.46375</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.49293</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.46098</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.37694</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.43882</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.51574</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.4183</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.54453</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.75979</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.34563</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34532</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.36045</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.7662899999999999</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.34382</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.27861</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.33837</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.483</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.39383</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.54406</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.50088</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.35101</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.36048</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.71992</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.5529299999999999</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.45049</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>1.01792</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.48215</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.44277</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.09119</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>1.12687</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.07996</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.36919</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1.11066</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>1.1273</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.01724</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.19299</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.14126</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.1302</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.17569</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.84184</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.19051</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.84804</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.34004</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.90128</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.70748</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.75587</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.9468799999999999</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.59644</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.7329600000000001</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.7219099999999999</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.80601</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.6196</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36016</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.7601599999999999</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.41339</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.76306</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.42773</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.7079299999999999</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.96147</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.95014</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.72073</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.70304</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.88301</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.89878</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.9055</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.72765</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.92818</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.72489</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.89795</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.65563</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.58414</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.58784</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.5878</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.65762</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.48061</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.58225</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.46992</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.7702899999999999</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.6282799999999999</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.5824199999999999</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.88437</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.66353</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.11138</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.79914</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.7618400000000001</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>1.30004</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>1.36051</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.74301</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.665</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.369</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>1.00503</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.61116</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.50084</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.50107</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.5488200000000001</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.60039</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.7516699999999999</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>1.20133</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.7060299999999999</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.9389500000000001</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.68089</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.96073</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.90495</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.76415</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.73384</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>1.18569</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.18687</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.45051</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.26422</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.66532</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.24896</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.2937</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.11313</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.43635</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>1.0416</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.9890399999999999</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.92116</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.44933</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.35319</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.70075</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.4994</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.5847899999999999</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.47768</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42656</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44839</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41786</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45773</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40707</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38858</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37684</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36649</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.44966</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.48779</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.40529</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.53208</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.53483</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.79902</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.68431</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.66674</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.50372</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>1.08579</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.69187</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.66535</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.8025099999999999</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.08204</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.19463</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.50018</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.19871</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.54673</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.15916</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.55744</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.5707899999999999</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.42748</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.50198</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.23503</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.34276</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.37364</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.42947</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.48249</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.46298</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.5069900000000001</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.51097</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.46035</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41266</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.4333</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.54326</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.5212599999999999</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.60703</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38461</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4060299999999999</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40312</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36536</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39931</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38196</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39386</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36413</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.7611599999999999</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.13938</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.88283</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.77419</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.5143799999999999</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.44751</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.42208</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37699</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.41272</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.40037</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.39972</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.3811</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.34298</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32961</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.42015</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.34773</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.35257</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.42079</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.43642</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.38377</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.5009400000000001</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.32586</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04337</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.36758</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.34279</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.34248</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.34304</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.46307</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.31043</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.3056</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.3258</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.45013</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.29946</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.3766600000000001</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.41296</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.44646</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.59069</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.48403</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.44986</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.4002</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.46389</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.45066</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.46497</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.5541699999999999</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.39282</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.45013</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.4254</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39849</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.3771600000000001</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.46141</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.42031</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.46929</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.70651</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.66814</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.67284</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.69126</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.6525</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.5032300000000001</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.45192</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.40126</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.40077</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.34642</v>
+      </c>
+      <c r="C136" t="n">
+        <v>1.0587</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.50184</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.7064400000000001</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.50295</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.50242</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.63409</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.62775</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.6226699999999999</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.6223500000000001</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.34478</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.34477</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.34529</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.34278</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.34441</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.34515</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.3444700000000001</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.34473</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.37244</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.38345</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.23463</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.30768</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.27322</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.38888</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.38851</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.34565</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.32629</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.30057</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.30644</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.31634</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.15489</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.7383999999999999</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.21616</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.38783</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.30182</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.27352</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.14179</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.4529</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.34276</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.40167</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.6999299999999999</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.56831</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.30638</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.29056</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.3078</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.32231</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.5001100000000001</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.38776</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.37521</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.39207</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.77749</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.36669</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.39287</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.36747</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.38318</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.40013</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.37221</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.40019</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.38307</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.45217</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.45135</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.45153</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.40039</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.39322</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.38317</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.39334</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.38272</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.42909</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.80888</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.38379</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.46819</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.39335</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.38944</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.3894</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.38615</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.40283</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.37115</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.49085</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.10354</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.38632</v>
+      </c>
+      <c r="E137" t="n">
+        <v>1.2093</v>
+      </c>
+      <c r="F137" t="n">
+        <v>1.09644</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.5262</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.76125</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.76102</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.51559</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.41797</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.42967</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.42738</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.40947</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.41659</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.39608</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.38834</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.44552</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.55976</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.36048</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.42766</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.38911</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.44513</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.70257</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>1.31899</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.42614</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.7740199999999999</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.8045099999999999</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.45541</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.40372</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.76074</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.41266</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.52974</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.48649</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.48984</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.24474</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>1.08909</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.98764</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.31791</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.6370800000000001</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.55203</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.38918</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.49814</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.58401</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.76135</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.5510900000000001</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.5497799999999999</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.39691</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.23713</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.36258</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.76225</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.5852200000000001</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.45297</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.49863</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>1.01424</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.77279</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.6286</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.7614</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>1.20559</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.60912</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.75176</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.6399199999999999</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>1.26896</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.90232</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.88662</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.90708</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.92565</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>1.17738</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.65142</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.96047</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.69512</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.98641</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.66035</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.67918</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.76072</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.66083</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.26507</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1.04528</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>1.02662</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.03573</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.54969</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.36567</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.0591</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.41072</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.3816000000000001</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.76048</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.39004</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.34554</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.5599</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.8079</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.5529500000000001</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.75725</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.7590800000000001</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.56253</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.47095</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.46044</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.40814</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.42957</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.42023</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.37102</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.38707</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.38385</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.36873</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.36063</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.36195</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.38359</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.4233</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.40587</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.42781</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.6388400000000001</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.59613</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.5642699999999999</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.5432</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.45285</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.48202</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.50037</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.5606100000000001</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.8138</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.17826</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.13388</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.04677</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>1.1366</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.75065</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.74539</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.05761</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>1.07597</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.68437</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.55457</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.56145</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.48012</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.28864</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.48495</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.5500900000000001</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.55053</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.5470900000000001</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.66231</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.55661</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>1.05269</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.66338</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.55028</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.50017</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.5004</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.48306</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.50025</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.48269</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.5004700000000001</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.5786</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.55823</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.5619700000000001</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.49851</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.5144299999999999</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.40357</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.38459</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.42362</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.5009400000000001</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.56198</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.66208</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>1.17632</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>1.07981</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.6627000000000001</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.58401</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>1.16592</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.8716499999999999</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.66225</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>1.16429</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.83877</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.49736</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.51227</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.49965</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.44002</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.53562</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.39202</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34455</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="D139" t="n">
+        <v>1.07486</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.7734800000000001</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.7811900000000001</v>
+      </c>
+      <c r="G139" t="n">
+        <v>1.21479</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.77424</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.5017699999999999</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.42146</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.40033</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.4202</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.42104</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35826</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.39343</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.37967</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.36491</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.36322</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.35317</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.35415</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.36165</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.34349</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.36237</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.38749</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.63024</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.59015</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.42788</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.64293</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.03226</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.21757</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.9344199999999999</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.98751</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>1.03499</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.97824</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.94564</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.97626</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.9591000000000001</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.94378</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.9462699999999999</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.4822</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.86987</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>1.24403</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.76546</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>1.32502</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>1.30688</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.72909</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.94921</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.8693099999999999</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.93626</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.54973</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.2161</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.71423</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.7005</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.59514</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.33699</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.73124</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.7358899999999999</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.80548</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.40407</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.6381</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.35607</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.48434</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.43909</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.65022</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.4552</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.40067</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.40151</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.41287</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.7073200000000001</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42434</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.69047</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.54891</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40169</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45852</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.6928</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.74175</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.70072</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36323</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.3687</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.76122</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40113</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40117</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.3757799999999999</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36465</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.40372</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.38905</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.7109099999999999</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.4658</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.75042</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.52446</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.51098</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.44386</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>1.02575</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.9234600000000001</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>1.03576</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.93384</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>1.04359</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>1.02642</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>1.0266</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1.39095</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1.09657</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>1.31682</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.6741200000000001</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.38981</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.68163</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.35741</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.6254700000000001</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.73777</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.7227899999999999</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>1.02297</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.72326</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.77628</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>1.14979</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1.44379</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.6582</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.4253</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.59011</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>1.18402</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.62722</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.60645</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.64835</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.65017</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39832</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.8131699999999999</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.7690499999999999</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.80865</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.8200599999999999</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37511</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27097</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.5004999999999999</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.38845</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.36768</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.35524</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.76049</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34959</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.4397799999999999</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.4398</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.37978</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.37973</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.35903</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.36067</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.36701</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.35732</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.38084</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.37295</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.50008</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37698</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35566</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.35838</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.34284</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.38193</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.40798</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.83411</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.52574</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.45585</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.48208</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.5605800000000001</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.68838</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.44099</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.38609</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.3917</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.46654</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.21384</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.21511</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.14766</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.5640499999999999</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.32904</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.70094</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1.09266</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.56904</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.44717</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.5258700000000001</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.44626</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.36878</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.45926</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.36438</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.37836</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.45138</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.3745</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.46028</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.39777</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.49994</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.49982</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.49744</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.5629500000000001</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1.06655</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.64927</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>1.04803</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>1.05863</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.18259</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.68579</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.50056</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.20147</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.29831</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.69179</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.54823</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>1.11743</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.09806</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.44799</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.45423</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.71554</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.17177</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.44499</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.38947</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.38042</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.37374</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37108</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.35637</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.33642</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.34472</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.07008</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.83449</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.83197</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.60775</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.58953</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.48131</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.51928</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.5473300000000001</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39872</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.4945</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.49469</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.52585</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.54726</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.5257200000000001</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.39325</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38503</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.5367499999999999</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.52543</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.5257000000000001</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.52606</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.52573</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.51593</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.50059</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.50075</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.49625</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.49524</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.37235</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.84801</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.50451</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.37418</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.50685</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.52337</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.5257000000000001</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.5194099999999999</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.5884299999999999</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.57037</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.48596</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.47699</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.69785</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.85148</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.9956</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.9826900000000001</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.9806</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.09393</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.7917000000000001</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.54401</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.55001</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.26086</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.22437</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>1.02587</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.36808</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.40689</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.7692</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.29981</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.4898</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.49501</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.51876</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.50497</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.48832</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.54173</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.67761</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.6195499999999999</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.05641</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.7142999999999999</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.72447</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.41788</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.60082</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.61375</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.62103</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.00515</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.65097</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.6252300000000001</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.7311799999999999</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.6522100000000001</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.64791</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.03826</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.77649</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.78371</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.80899</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.08966</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.64879</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.64815</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.73017</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.6338200000000001</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.91839</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.69574</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.58854</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.58539</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.5436799999999999</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.38087</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.75566</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.63476</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.63527</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.53477</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.53432</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.53599</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.51535</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.55376</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41962</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.5210399999999999</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.5011100000000001</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.45963</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.45987</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.38096</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.43855</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.39902</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.41203</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.49492</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.49899</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.54737</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.51981</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.52011</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.5257200000000001</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.62097</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.56956</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.01707</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.42089</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.7256900000000001</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.50815</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.52722</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.5651900000000001</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.5586100000000001</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.5314099999999999</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.56586</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.5045299999999999</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.52128</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.5455599999999999</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.61924</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.5367999999999999</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.52452</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.6784199999999999</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.52391</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.52498</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.5280900000000001</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.5581699999999999</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.5249299999999999</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.5575</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.56421</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.6085499999999999</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.55723</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.54257</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.62763</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.60924</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.61405</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.62659</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.62862</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.5618300000000001</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.55357</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.54695</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.5620299999999999</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.43435</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.73349</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.83308</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.81647</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.6216900000000001</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.81549</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.7645299999999999</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.6950700000000001</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.64175</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.60894</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.6503300000000001</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.64606</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.6203099999999999</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.61615</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.71949</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.67843</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.8277599999999999</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.70382</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.60798</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.53089</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.5123799999999999</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40856</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40972</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38405</v>
       </c>
     </row>
   </sheetData>
